--- a/backend/automated_tests/test_cases.xlsx
+++ b/backend/automated_tests/test_cases.xlsx
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Data exported successfully. File name: export_2026-06-11.csv saved to server.</t>
+          <t>Data exported successfully. File name: export_2026-06-16.csv saved to server.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Access blocked. HTTP 302. Redirect Location: http://localhost/rct-education-web/frontend/auth/login.php</t>
+          <t>Access blocked. HTTP 302. Redirect Location: http://localhost/rct-education-web/frontend_php_backup/auth/login.php</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
